--- a/reports/集团总公司_现金流量表_2026-06.xlsx
+++ b/reports/集团总公司_现金流量表_2026-06.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>177085428</v>
+        <v>174824759</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1139156928</v>
+        <v>1119006208</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4113080</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>23342721</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2074509</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>11663247</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1027207</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>5834430</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>829814</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>4666534</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>616948</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>3499654</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>414114</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>2333919</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>309289</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1749403</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>206423</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1167172</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>517128</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>2915377</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>258581</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1466459</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>164821</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>927016</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>562277</v>
+        <v>549388</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>3177138</v>
+        <v>3120347</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3819240</v>
+        <v>3773024</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>21580560</v>
+        <v>21211054</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>181466945</v>
+        <v>189679085</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>127308000</v>
+        <v>125241947</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>719352000</v>
+        <v>706820534</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1373313</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>7781350</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1036090</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>5830960</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>685134</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>3890238</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>518748</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>2916041</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>342439</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1944633</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>260533</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1465910</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>25673780</v>
+        <v>25106309</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>145069320</v>
+        <v>142299919</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11882080</v>
+        <v>11687838</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>67139520</v>
+        <v>65938226</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5410590</v>
+        <v>5306948</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>30572460</v>
+        <v>29984188</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>170274450</v>
+        <v>171559299</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>11192495</v>
+        <v>18119786</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>242025</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1483200</v>
+        <v>1458121</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2121048</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>12978000</v>
+        <v>12742320</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1294720</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>7910400</v>
+        <v>7771740</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2363073</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20115562</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>123600000</v>
+        <v>121120027</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2936439</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>17922000</v>
+        <v>17538138</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14265189</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>87756000</v>
+        <v>86036031</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>524738</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>3213600</v>
+        <v>3155805</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20640300</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18277227</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4777055</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>29046000</v>
+        <v>28550416</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7627667</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>46350000</v>
+        <v>45527010</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7552825</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>46350000</v>
+        <v>45549704</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>244050</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1483200</v>
+        <v>1457827</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12648772</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6186853</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>37698000</v>
+        <v>37053564</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6172863</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>37698000</v>
+        <v>37042803</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1010721</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>6180000</v>
+        <v>6073650</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>877037</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>5376600</v>
+        <v>5284780</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>127096</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>772500</v>
+        <v>758760</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7324670</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5324102</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>-2161455</v>
+        <v>5166661</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>-2161455</v>
+        <v>5166661</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
